--- a/data/trans_dic/IP31KM10_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM10_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>65,22%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,18; 77,18</t>
+          <t>50,56; 74,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,83; 73,2</t>
+          <t>55,78; 79,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,21; 70,97</t>
+          <t>56,48; 73,7</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,15%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,32; 63,26</t>
+          <t>56,11; 65,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,18; 63,51</t>
+          <t>49,48; 57,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,78; 61,34</t>
+          <t>54,17; 60,24</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,78; 45,13</t>
+          <t>41,76; 55,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,47; 55,19</t>
+          <t>33,06; 47,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,73; 48,86</t>
+          <t>39,21; 48,98</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,22; 59,24</t>
+          <t>54,18; 61,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,95; 60,33</t>
+          <t>47,87; 54,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,83; 57,84</t>
+          <t>52,26; 57,17</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33931</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>31254</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69635</t>
+          <t>64975</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21579; 41443</t>
+          <t>27157; 39871</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29072; 42711</t>
+          <t>25608; 36337</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56258; 79522</t>
+          <t>56265; 73424</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>328</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>250192</t>
+          <t>282417</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>297482</t>
+          <t>226879</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>547674</t>
+          <t>509296</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>227340; 285826</t>
+          <t>261691; 303186</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>273761; 320904</t>
+          <t>210144; 244236</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514754; 587109</t>
+          <t>482721; 536768</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56850</t>
+          <t>80826</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86634</t>
+          <t>58152</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143483</t>
+          <t>138977</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46457; 65974</t>
+          <t>69610; 91874</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73311; 99963</t>
+          <t>48652; 69351</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126779; 159928</t>
+          <t>123044; 153704</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>458</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>340973</t>
+          <t>396963</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>419820</t>
+          <t>316285</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>760793</t>
+          <t>713249</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>314284; 386050</t>
+          <t>372106; 422138</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>394361; 449275</t>
+          <t>295711; 338404</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>723831; 807651</t>
+          <t>681789; 745817</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM10_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM10_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman frutos secos con regularidad (al menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>62,78%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>68,08%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>65,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>50,56; 74,23</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55,78; 79,16</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56,48; 73,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>60,55%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53,43%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>56,11; 65,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>49,48; 57,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54,17; 60,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>48,49%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>39,52%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>44,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>41,76; 55,12</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>33,06; 47,13</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>39,21; 48,98</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>57,8%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>51,2%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>54,18; 61,46</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>47,87; 54,78</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52,26; 57,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6277668264165766</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.6808480125479859</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6522266974314505</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>33720</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>31254</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>64975</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.5055672814514623</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.5578389623570672</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5647970136452791</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>27157; 39871</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>25608; 36337</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56265; 73424</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7422775554139376</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7915721798239943</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7370437987593681</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.6054959822421009</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.5342520187865589</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5715432655675767</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>282417</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>226879</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>509296</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5610589929010343</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4948462632399991</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.5417198110192943</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>261691; 303186</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>210144; 244236</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>482721; 536768</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.6500240507485769</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5751258856483719</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.6023728163591568</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4848970768320583</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3952177684474958</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.442850155106641</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>80826</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>58152</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>138977</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4176131041689272</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3306499724181718</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3920790821645914</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>69610; 91874</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>48652; 69351</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>123044; 153704</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5511798540916276</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4713250385273107</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.4897746814963997</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5779695179639944</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5120280264557312</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5467455247549488</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>396963</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>316285</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>713249</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5417774523957127</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4787200861872445</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.5226296477243271</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>372106; 422138</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>295711; 338404</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>681789; 745817</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6146233280482842</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5478346999011823</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5717108250807342</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman frutos secos con regularidad (al menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>33720</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>31254</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>64975</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>27157</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>25608</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>56265</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>39871</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>36337</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>73424</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>328</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>282417</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>226879</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>509296</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>261691</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>210144</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>482721</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>303186</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>244236</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>536768</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>80826</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>58152</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>138977</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>69610</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>48652</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>123044</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>91874</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>69351</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>153704</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>519</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>458</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>396963</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>316285</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>713249</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>372106</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>295711</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>681789</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>422138</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>338404</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>745817</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>